--- a/WAR3修仙项目/配置表格/__tables__.xlsx
+++ b/WAR3修仙项目/配置表格/__tables__.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7410" yWindow="4400" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,6 +27,7 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
+      <family val="3"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -34,6 +35,7 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -433,7 +435,7 @@
     <col width="20.33203125" customWidth="1" style="3" min="2" max="2"/>
     <col width="15.6640625" customWidth="1" style="3" min="3" max="3"/>
     <col width="32.33203125" customWidth="1" style="3" min="4" max="4"/>
-    <col width="24.33203125" customWidth="1" style="3" min="5" max="5"/>
+    <col width="30.5" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
     <col width="18" customWidth="1" style="3" min="6" max="9"/>
   </cols>
   <sheetData>
@@ -583,15 +585,15 @@
         </is>
       </c>
     </row>
-    <row r="4" s="3">
+    <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tbitem</t>
+          <t>TbRegionConfig</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>RegionConfig</t>
         </is>
       </c>
       <c r="D4" s="0" t="b">
@@ -599,115 +601,115 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>道具demo.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>region_config@C场景区域配置.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>config_id</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>场景区域配置</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>region_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TbSceneConfig</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SceneConfig</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ConfigScene@C场景区域配置.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>config_id</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>场景配置</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>scene_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TbDropConfig</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DropConfig</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>drop_config@D掉落方案.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>道具表</t>
-        </is>
-      </c>
-      <c r="K4" s="0" t="inlineStr">
-        <is>
-          <t>tb_item</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" s="3">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>TbLang</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>Lang</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>多语言.xlsx</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>多语言表</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>tb_lang</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" s="3">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>TbRegionConfig</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>RegionConfig</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>region_config@C场景区域配置.xlsx</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>config_id</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="n"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>场景区域配置</t>
+          <t>掉落方案</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>region_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" s="3">
+          <t>drop_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TbConfigScene</t>
+          <t>TbMonsterConfig</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ConfigScene</t>
+          <t>MonsterConfig</t>
         </is>
       </c>
       <c r="D7" s="0" t="b">
@@ -715,10 +717,10 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ConfigScene@C场景区域配置.xlsx</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>monster_config@G怪物表.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>config_id</t>
         </is>
@@ -726,24 +728,24 @@
       <c r="H7" s="0" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>场景配置</t>
+          <t>怪物表</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>ConfigScene</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" s="3">
+          <t>monster_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TbDropConfig</t>
+          <t>TbSpawnConfig</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DropConfig</t>
+          <t>SpawnConfig</t>
         </is>
       </c>
       <c r="D8" s="0" t="b">
@@ -751,35 +753,39 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>drop_config@D掉落方案.xlsx</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="n"/>
+          <t>spawn_config@G怪物刷新配置.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>config_id</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>掉落方案</t>
+          <t>怪物刷新配置</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>drop_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" s="3">
+          <t>spawn_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TbMonsterConfig</t>
+          <t>TbPlayerAttrConfig</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MonsterConfig</t>
+          <t>PlayerAttrConfig</t>
         </is>
       </c>
       <c r="D9" s="0" t="b">
@@ -787,35 +793,35 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>monster_config@G怪物表.xlsx</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ConfigID</t>
+          <t>init_char_config@J角色属性表.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>level</t>
         </is>
       </c>
       <c r="H9" s="0" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>怪物表</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>monster_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" s="3">
+          <t>角色属性表</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>player_attr_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TbSpawnConfig</t>
+          <t>TbAttrConfig</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SpawnConfig</t>
+          <t>AttrConfig</t>
         </is>
       </c>
       <c r="D10" s="0" t="b">
@@ -823,10 +829,10 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>spawn_config@G怪物刷新配置.xlsx</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>attr_config@S属性配置表.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>config_id</t>
         </is>
@@ -834,24 +840,24 @@
       <c r="H10" s="0" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>怪物刷新配置</t>
+          <t>属性配置表</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>spawn_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" s="3">
+          <t>attr_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TbInitCharConfig</t>
+          <t>TbItemConfig</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>InitCharConfig</t>
+          <t>ItemConfig</t>
         </is>
       </c>
       <c r="D11" s="0" t="b">
@@ -859,35 +865,35 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>init_char_config@J角色属性表.xlsx</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Level</t>
+          <t>item_config@W物品表.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="H11" s="0" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>角色属性表</t>
+          <t>物品表</t>
         </is>
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>init_char_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" s="3">
+          <t>item_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TbAttrConfig</t>
+          <t>TbEquipConfig</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AttrConfig</t>
+          <t>EquipConfig</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
@@ -895,35 +901,35 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>attr_config@S属性配置表.xlsx</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ConfigID</t>
+          <t>equip_config@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="H12" s="0" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>属性配置表</t>
-        </is>
-      </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>attr_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" s="3">
+          <t>装备表</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>equip_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TbItemConfig</t>
+          <t>TbEquipQianghuaConfig</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ItemConfig</t>
+          <t>EquipQianghuaConfig</t>
         </is>
       </c>
       <c r="D13" s="0" t="b">
@@ -931,35 +937,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>item_config@W物品表.xlsx</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ID</t>
+          <t>ConfigQianghua@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>reinforcement_id</t>
         </is>
       </c>
       <c r="H13" s="0" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>物品表</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>item_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" s="3">
+          <t>装备强化配置</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>equip_qianghua_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TbEquipConfig</t>
+          <t>TbEquipXiaojipinConfig</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EquipConfig</t>
+          <t>EquipXiaojipinConfig</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
@@ -967,35 +973,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>equip_config@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="n"/>
+          <t>ConfigXiaojiping@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>hidden_attribute</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>装备表</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>equip_config</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" s="3">
+          <t>装备小极品配置</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>equip_xiaojipin_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>TbConfigQianghua</t>
+          <t>TbEquipLianhuaConfig</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ConfigQianghua</t>
+          <t>EquipLianhuaConfig</t>
         </is>
       </c>
       <c r="D15" s="0" t="b">
@@ -1003,35 +1013,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ConfigQianghua@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ReinforcementId</t>
+          <t>ConfigLianhua@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>hidden_attribute</t>
         </is>
       </c>
       <c r="H15" s="0" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>装备强化配置</t>
-        </is>
-      </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>ConfigQianghua</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" s="3">
+          <t>装备炼化配置</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>equip_lianhua_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TbConfigXiaojiping</t>
+          <t>TbEquipAffixConfig</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ConfigXiaojiping</t>
+          <t>EquipAffixConfig</t>
         </is>
       </c>
       <c r="D16" s="0" t="b">
@@ -1039,35 +1049,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ConfigXiaojiping@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>HiddenAttribute</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="n"/>
+          <t>ConfigCitiao@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>hidden_affix</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>装备小极品配置</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>ConfigXiaojiping</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" s="3">
+          <t>装备词条掉落配置</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>equip_affix_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TbConfigLianhua</t>
+          <t>TbEquipTaozhuangConfig</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ConfigLianhua</t>
+          <t>EquipTaozhuangConfig</t>
         </is>
       </c>
       <c r="D17" s="0" t="b">
@@ -1075,95 +1089,105 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ConfigLianhua@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>HiddenAttribute</t>
+          <t>ConfigTaozhuang@Z装备.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>suit_id</t>
         </is>
       </c>
       <c r="H17" s="0" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>装备炼化配置</t>
-        </is>
-      </c>
-      <c r="K17" s="0" t="inlineStr">
-        <is>
-          <t>ConfigLianhua</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" s="3">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>TbConfigCitiao</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCitiao</t>
+          <t>装备套装配置</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>equip_taozhuang_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>TbSkillConfig</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>SkillConfig</t>
         </is>
       </c>
       <c r="D18" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCitiao@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>HiddenAffix</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>装备词条配置</t>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>skill_config@J技能BUFF表.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>技能配置</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>ConfigCitiao</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" s="3">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>TbConfigTaozhuang</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>ConfigTaozhuang</t>
+          <t>skill_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>TbBuffConfig</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>BuffConfig</t>
         </is>
       </c>
       <c r="D19" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>ConfigTaozhuang@Z装备.xlsx</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SuitID</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>装备套装配置</t>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>buff_config@J技能BUFF表.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>BUFF配置</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>ConfigTaozhuang</t>
+          <t>buff_config</t>
         </is>
       </c>
     </row>
